--- a/ig/DM-37/ValueSet-JDV-J220-FonctionContact-ROR.xlsx
+++ b/ig/DM-37/ValueSet-JDV-J220-FonctionContact-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="83">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-30T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,6 +247,12 @@
   </si>
   <si>
     <t>Coordonnateur de la gestion des risques associés aux soins</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Responsable du Bed Management</t>
   </si>
   <si>
     <t/>
@@ -525,7 +531,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -737,15 +743,23 @@
         <v>78</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>80</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
